--- a/experiment/ELAN_bestx2/Test/results-Set14/Set14.xlsx
+++ b/experiment/ELAN_bestx2/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.39</v>
+        <v>26.45</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7486</v>
+        <v>0.7954</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.59</v>
+        <v>28.75</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8698</v>
+        <v>0.8917</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.57</v>
+        <v>29.48</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8413</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.03</v>
+        <v>31.13</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8408</v>
+        <v>0.8557</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.01</v>
+        <v>29.94</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8881</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.4</v>
+        <v>35.98</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8802</v>
+        <v>0.8905</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.37</v>
+        <v>34.86</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9198</v>
+        <v>0.9498</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.04</v>
+        <v>37.32</v>
       </c>
       <c r="C9" t="n">
-        <v>0.955</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35.61</v>
+        <v>37.33</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9237</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.94</v>
+        <v>31.54</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8719</v>
+        <v>0.8981</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.08</v>
+        <v>39.87</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9671</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>35.6</v>
+        <v>37.48</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9124</v>
+        <v>0.9237</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.05</v>
+        <v>34.42</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9589</v>
+        <v>0.9905</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.06</v>
+        <v>34.56</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9323</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.2</v>
+        <v>33.51</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.9171</v>
       </c>
     </row>
   </sheetData>
